--- a/bnc-streamlit-app/data/wcbonus.xlsx
+++ b/bnc-streamlit-app/data/wcbonus.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wt_an\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/557e8c8e9b1f0372/WC 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F28F3C6-4D2D-4ADF-BF8C-925EF8F1ED0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{DFFFCD4A-50E4-47AC-AFE8-5366D054BD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{060B93FD-5BA1-4B90-94F4-7E3D8EC25C08}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{96B625A3-712C-4A8D-A678-5DC164D388B8}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$145</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="305">
   <si>
     <t>Manager</t>
   </si>
@@ -954,6 +954,9 @@
   </si>
   <si>
     <t>Winner</t>
+  </si>
+  <si>
+    <t>Golden Glove</t>
   </si>
 </sst>
 </file>
@@ -1373,7 +1376,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{508FC116-B6A7-49C3-8901-C290189AEBC3}">
-  <dimension ref="A1:I145"/>
+  <dimension ref="A1:J145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1381,7 +1384,7 @@
     <col min="3" max="3" width="27.7109375" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1407,10 +1410,13 @@
         <v>302</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1421,14 +1427,14 @@
         <v>5</v>
       </c>
       <c r="D2">
-        <f>SUM(E2:I2)</f>
+        <f>SUM(E2:J2)</f>
         <v>5</v>
       </c>
       <c r="G2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -1439,11 +1445,11 @@
         <v>8</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D66" si="0">SUM(E3:I3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D3:D66" si="0">SUM(E3:J3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1455,10 +1461,13 @@
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -1470,10 +1479,13 @@
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1488,7 +1500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
@@ -1503,7 +1515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -1518,7 +1530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
@@ -1533,7 +1545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -1548,7 +1560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1563,7 +1575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1578,7 +1590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -1593,7 +1605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -1608,7 +1620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
@@ -1626,7 +1638,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
@@ -1644,7 +1656,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>3</v>
       </c>
@@ -1659,7 +1671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
@@ -1677,7 +1689,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -1692,7 +1704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>21</v>
       </c>
@@ -1707,7 +1719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>24</v>
       </c>
@@ -1722,7 +1734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>3</v>
       </c>
@@ -1737,7 +1749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
@@ -1752,7 +1764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>9</v>
       </c>
@@ -1767,7 +1779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>12</v>
       </c>
@@ -1782,7 +1794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>12</v>
       </c>
@@ -1794,10 +1806,13 @@
       </c>
       <c r="D26">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="J26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>9</v>
       </c>
@@ -1815,7 +1830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
@@ -1830,7 +1845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>3</v>
       </c>
@@ -1845,7 +1860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>24</v>
       </c>
@@ -1860,7 +1875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>21</v>
       </c>
@@ -1878,7 +1893,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>18</v>
       </c>
@@ -1893,7 +1908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>15</v>
       </c>
@@ -1908,7 +1923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
@@ -1920,10 +1935,13 @@
       </c>
       <c r="D34">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="J34">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>3</v>
       </c>
@@ -1938,7 +1956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>12</v>
       </c>
@@ -1953,7 +1971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>9</v>
       </c>
@@ -1965,13 +1983,19 @@
       </c>
       <c r="D37">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I37">
+        <v>5</v>
+      </c>
+      <c r="J37">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>18</v>
       </c>
@@ -1986,7 +2010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>15</v>
       </c>
@@ -2001,7 +2025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>24</v>
       </c>
@@ -2016,7 +2040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>21</v>
       </c>
@@ -2031,7 +2055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>21</v>
       </c>
@@ -2049,7 +2073,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>24</v>
       </c>
@@ -2064,7 +2088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>15</v>
       </c>
@@ -2079,7 +2103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>18</v>
       </c>
@@ -2097,7 +2121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>9</v>
       </c>
@@ -2109,13 +2133,16 @@
       </c>
       <c r="D46">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E46">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="J46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>12</v>
       </c>
@@ -2133,7 +2160,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>3</v>
       </c>
@@ -2148,7 +2175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
@@ -2163,7 +2190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>18</v>
       </c>
@@ -2175,10 +2202,13 @@
       </c>
       <c r="D50">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="J50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>15</v>
       </c>
@@ -2193,7 +2223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>24</v>
       </c>
@@ -2211,7 +2241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>21</v>
       </c>
@@ -2223,10 +2253,16 @@
       </c>
       <c r="D53">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="F53">
+        <v>5</v>
+      </c>
+      <c r="J53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>6</v>
       </c>
@@ -2241,7 +2277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>3</v>
       </c>
@@ -2256,7 +2292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>12</v>
       </c>
@@ -2271,7 +2307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>9</v>
       </c>
@@ -2286,7 +2322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>9</v>
       </c>
@@ -2301,7 +2337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>12</v>
       </c>
@@ -2316,7 +2352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>3</v>
       </c>
@@ -2328,10 +2364,13 @@
       </c>
       <c r="D60">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="J60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>6</v>
       </c>
@@ -2346,7 +2385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>21</v>
       </c>
@@ -2358,10 +2397,13 @@
       </c>
       <c r="D62">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="J62">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>24</v>
       </c>
@@ -2376,7 +2418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>15</v>
       </c>
@@ -2388,7 +2430,10 @@
       </c>
       <c r="D64">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="J64">
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -2432,7 +2477,7 @@
         <v>142</v>
       </c>
       <c r="D67">
-        <f t="shared" ref="D67:D130" si="1">SUM(E67:I67)</f>
+        <f t="shared" ref="D67:D130" si="1">SUM(E67:J67)</f>
         <v>0</v>
       </c>
     </row>
@@ -2634,7 +2679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>9</v>
       </c>
@@ -2649,7 +2694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>21</v>
       </c>
@@ -2664,7 +2709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>24</v>
       </c>
@@ -2679,7 +2724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>15</v>
       </c>
@@ -2694,7 +2739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>18</v>
       </c>
@@ -2709,7 +2754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>9</v>
       </c>
@@ -2724,7 +2769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>12</v>
       </c>
@@ -2742,7 +2787,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>3</v>
       </c>
@@ -2757,7 +2802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>6</v>
       </c>
@@ -2772,7 +2817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>6</v>
       </c>
@@ -2787,7 +2832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>3</v>
       </c>
@@ -2802,7 +2847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>12</v>
       </c>
@@ -2817,7 +2862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>9</v>
       </c>
@@ -2832,7 +2877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>18</v>
       </c>
@@ -2850,7 +2895,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>15</v>
       </c>
@@ -2865,7 +2910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>24</v>
       </c>
@@ -2877,13 +2922,16 @@
       </c>
       <c r="D96">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E96">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="J96">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>21</v>
       </c>
@@ -2898,7 +2946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>12</v>
       </c>
@@ -2913,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>9</v>
       </c>
@@ -2928,7 +2976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>6</v>
       </c>
@@ -2943,7 +2991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>3</v>
       </c>
@@ -2958,7 +3006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>24</v>
       </c>
@@ -2970,10 +3018,13 @@
       </c>
       <c r="D102">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="J102">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>21</v>
       </c>
@@ -2988,7 +3039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>18</v>
       </c>
@@ -3003,7 +3054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>15</v>
       </c>
@@ -3018,7 +3069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>15</v>
       </c>
@@ -3033,7 +3084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>18</v>
       </c>
@@ -3045,10 +3096,13 @@
       </c>
       <c r="D107">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="J107">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>21</v>
       </c>
@@ -3063,7 +3117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>24</v>
       </c>
@@ -3078,7 +3132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>3</v>
       </c>
@@ -3093,7 +3147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>6</v>
       </c>
@@ -3108,7 +3162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>9</v>
       </c>
@@ -3123,7 +3177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>12</v>
       </c>
@@ -3138,7 +3192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>24</v>
       </c>
@@ -3156,7 +3210,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>21</v>
       </c>
@@ -3174,7 +3228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>18</v>
       </c>
@@ -3189,7 +3243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>15</v>
       </c>
@@ -3204,7 +3258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>12</v>
       </c>
@@ -3219,7 +3273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>9</v>
       </c>
@@ -3234,7 +3288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>6</v>
       </c>
@@ -3252,7 +3306,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>3</v>
       </c>
@@ -3264,10 +3318,13 @@
       </c>
       <c r="D121">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="J121">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>3</v>
       </c>
@@ -3285,7 +3342,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>6</v>
       </c>
@@ -3300,7 +3357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>9</v>
       </c>
@@ -3318,7 +3375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>12</v>
       </c>
@@ -3333,7 +3390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>15</v>
       </c>
@@ -3345,10 +3402,13 @@
       </c>
       <c r="D126">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="J126">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>18</v>
       </c>
@@ -3363,7 +3423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>21</v>
       </c>
@@ -3378,7 +3438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>24</v>
       </c>
@@ -3393,7 +3453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
         <v>3</v>
       </c>
@@ -3408,7 +3468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
         <v>21</v>
       </c>
@@ -3419,11 +3479,11 @@
         <v>270</v>
       </c>
       <c r="D131">
-        <f t="shared" ref="D131:D145" si="2">SUM(E131:I131)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+        <f t="shared" ref="D131:D145" si="2">SUM(E131:J131)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>6</v>
       </c>
@@ -3438,7 +3498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
         <v>12</v>
       </c>
@@ -3453,7 +3513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
         <v>9</v>
       </c>
@@ -3468,7 +3528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
         <v>24</v>
       </c>
@@ -3483,7 +3543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
         <v>15</v>
       </c>
@@ -3498,7 +3558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
         <v>18</v>
       </c>
@@ -3513,7 +3573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
         <v>21</v>
       </c>
@@ -3528,7 +3588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
         <v>3</v>
       </c>
@@ -3540,10 +3600,13 @@
       </c>
       <c r="D139">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+      <c r="J139">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
         <v>24</v>
       </c>
@@ -3558,7 +3621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
         <v>12</v>
       </c>
@@ -3576,7 +3639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
         <v>6</v>
       </c>
@@ -3591,7 +3654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
         <v>15</v>
       </c>
@@ -3606,7 +3669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
         <v>9</v>
       </c>
@@ -3621,7 +3684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
         <v>18</v>
       </c>
@@ -3633,11 +3696,14 @@
       </c>
       <c r="D145">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="J145">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I145" xr:uid="{508FC116-B6A7-49C3-8901-C290189AEBC3}"/>
+  <autoFilter ref="A1:J145" xr:uid="{508FC116-B6A7-49C3-8901-C290189AEBC3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>